--- a/www/terminologies/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="2455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="2527">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -597,12 +597,6 @@
     <t>Contrepulsion par ballon intraaortique (CPBIA)</t>
   </si>
   <si>
-    <t>0145</t>
-  </si>
-  <si>
-    <t>Coronarographie</t>
-  </si>
-  <si>
     <t>0146</t>
   </si>
   <si>
@@ -1773,12 +1767,6 @@
     <t>Thoracoscopie</t>
   </si>
   <si>
-    <t>0522</t>
-  </si>
-  <si>
-    <t>Prise en charge de la tuberculose</t>
-  </si>
-  <si>
     <t>0523</t>
   </si>
   <si>
@@ -3192,7 +3180,7 @@
     <t>0814</t>
   </si>
   <si>
-    <t>Soutien et écoute téléphonique</t>
+    <t>Soutien et écoute à distance (par téléphone et/ou par messagerie)</t>
   </si>
   <si>
     <t>0815</t>
@@ -5031,12 +5019,6 @@
     <t>Chirurgie percutanée du rein</t>
   </si>
   <si>
-    <t>1165</t>
-  </si>
-  <si>
-    <t>Chirurgie proctologique</t>
-  </si>
-  <si>
     <t>1167</t>
   </si>
   <si>
@@ -5829,18 +5811,6 @@
     <t>Échographie de datation de grossesse</t>
   </si>
   <si>
-    <t>1302</t>
-  </si>
-  <si>
-    <t>Echographie de mesure de la clarté nucale par PS agréé</t>
-  </si>
-  <si>
-    <t>1303</t>
-  </si>
-  <si>
-    <t>Échographie morphologique du 2ème trimestre</t>
-  </si>
-  <si>
     <t>1304</t>
   </si>
   <si>
@@ -6342,7 +6312,7 @@
     <t>1391</t>
   </si>
   <si>
-    <t>Maladies vectorielles à tique (Lyme…)</t>
+    <t>Prise en charge de maladies vectorielles à tique (Lyme…)</t>
   </si>
   <si>
     <t>1392</t>
@@ -6654,7 +6624,7 @@
     <t>1453</t>
   </si>
   <si>
-    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
+    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
   </si>
   <si>
     <t>1454</t>
@@ -7311,6 +7281,36 @@
     <t>Evaluation et suivi des addictions liées au chemsex (cathinones de synthèse, poppers, etc)</t>
   </si>
   <si>
+    <t>1565</t>
+  </si>
+  <si>
+    <t>Groupe « entendeurs de voix » - hallucinations auditives</t>
+  </si>
+  <si>
+    <t>1566</t>
+  </si>
+  <si>
+    <t>Groupe directives anticipées en psychiatrie</t>
+  </si>
+  <si>
+    <t>1567</t>
+  </si>
+  <si>
+    <t>Autodétermination par la participation des adhérents à la gestion de la structure</t>
+  </si>
+  <si>
+    <t>1568</t>
+  </si>
+  <si>
+    <t>Activités sociales, culturelles, sportives et de loisirs</t>
+  </si>
+  <si>
+    <t>1569</t>
+  </si>
+  <si>
+    <t>Dépôt de plainte sur site</t>
+  </si>
+  <si>
     <t>1570</t>
   </si>
   <si>
@@ -7369,6 +7369,222 @@
   </si>
   <si>
     <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
+  </si>
+  <si>
+    <t>1580</t>
+  </si>
+  <si>
+    <t>Relayage courte durée (quelques heures par jour)</t>
+  </si>
+  <si>
+    <t>1581</t>
+  </si>
+  <si>
+    <t>Relayage longue durée (sur plusieurs jours)</t>
+  </si>
+  <si>
+    <t>1582</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en cardiologie</t>
+  </si>
+  <si>
+    <t>1583</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie cardiaque et gros vaisseaux</t>
+  </si>
+  <si>
+    <t>1584</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie digestive et viscérale</t>
+  </si>
+  <si>
+    <t>1585</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie maxillo-faciale et stomatologie</t>
+  </si>
+  <si>
+    <t>1586</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie orthopédique et traumatologie</t>
+  </si>
+  <si>
+    <t>1587</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique orthopédique et traumatologie</t>
+  </si>
+  <si>
+    <t>1588</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique viscérale et digestive</t>
+  </si>
+  <si>
+    <t>1589</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie thoracique et pulmonaire</t>
+  </si>
+  <si>
+    <t>1590</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie vasculaire</t>
+  </si>
+  <si>
+    <t>1591</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en dermatologie</t>
+  </si>
+  <si>
+    <t>1592</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en endocrinologie</t>
+  </si>
+  <si>
+    <t>1593</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gériatrie (gérontologie)</t>
+  </si>
+  <si>
+    <t>1594</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gynécologie</t>
+  </si>
+  <si>
+    <t>1595</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hématologie</t>
+  </si>
+  <si>
+    <t>1596</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hépato-gastro-entérologie</t>
+  </si>
+  <si>
+    <t>1597</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en maladies infectieuses et tropicales</t>
+  </si>
+  <si>
+    <t>1598</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine interne</t>
+  </si>
+  <si>
+    <t>1599</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine vasculaire</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en néphrologie (dont dialyse)</t>
+  </si>
+  <si>
+    <t>1601</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurochirurgie</t>
+  </si>
+  <si>
+    <t>1602</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurologie</t>
+  </si>
+  <si>
+    <t>1603</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oncologie</t>
+  </si>
+  <si>
+    <t>1604</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en ophtalmologie</t>
+  </si>
+  <si>
+    <t>1605</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
+  </si>
+  <si>
+    <t>1606</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pédiatrie</t>
+  </si>
+  <si>
+    <t>1607</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pneumologie</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en rhumatologie</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en urologie</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en caisson oxygène hyperbare</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie de la main SOS main</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en odontologie</t>
+  </si>
+  <si>
+    <t>1613</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en psychiatrie (dont équipe de liaison)</t>
+  </si>
+  <si>
+    <t>1614</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en radiologie interventionnelle</t>
+  </si>
+  <si>
+    <t>1615</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) rachis</t>
   </si>
   <si>
     <t/>
@@ -7639,7 +7855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1215"/>
+  <dimension ref="A1:B1251"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -17355,15 +17571,303 @@
         <v>2452</v>
       </c>
       <c r="B1214" t="s" s="2">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="s" s="2">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="B1215" t="s" s="2">
-        <v>2454</v>
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="s" s="2">
+        <v>2456</v>
+      </c>
+      <c r="B1216" t="s" s="2">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="s" s="2">
+        <v>2458</v>
+      </c>
+      <c r="B1217" t="s" s="2">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="s" s="2">
+        <v>2460</v>
+      </c>
+      <c r="B1218" t="s" s="2">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="s" s="2">
+        <v>2462</v>
+      </c>
+      <c r="B1219" t="s" s="2">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="s" s="2">
+        <v>2464</v>
+      </c>
+      <c r="B1220" t="s" s="2">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="s" s="2">
+        <v>2466</v>
+      </c>
+      <c r="B1221" t="s" s="2">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="s" s="2">
+        <v>2468</v>
+      </c>
+      <c r="B1222" t="s" s="2">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="s" s="2">
+        <v>2470</v>
+      </c>
+      <c r="B1223" t="s" s="2">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="s" s="2">
+        <v>2472</v>
+      </c>
+      <c r="B1224" t="s" s="2">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="s" s="2">
+        <v>2474</v>
+      </c>
+      <c r="B1225" t="s" s="2">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="s" s="2">
+        <v>2476</v>
+      </c>
+      <c r="B1226" t="s" s="2">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="s" s="2">
+        <v>2478</v>
+      </c>
+      <c r="B1227" t="s" s="2">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="s" s="2">
+        <v>2480</v>
+      </c>
+      <c r="B1228" t="s" s="2">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="s" s="2">
+        <v>2482</v>
+      </c>
+      <c r="B1229" t="s" s="2">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="s" s="2">
+        <v>2484</v>
+      </c>
+      <c r="B1230" t="s" s="2">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="s" s="2">
+        <v>2486</v>
+      </c>
+      <c r="B1231" t="s" s="2">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="s" s="2">
+        <v>2488</v>
+      </c>
+      <c r="B1232" t="s" s="2">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="s" s="2">
+        <v>2490</v>
+      </c>
+      <c r="B1233" t="s" s="2">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="s" s="2">
+        <v>2492</v>
+      </c>
+      <c r="B1234" t="s" s="2">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="s" s="2">
+        <v>2494</v>
+      </c>
+      <c r="B1235" t="s" s="2">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="s" s="2">
+        <v>2496</v>
+      </c>
+      <c r="B1236" t="s" s="2">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="s" s="2">
+        <v>2498</v>
+      </c>
+      <c r="B1237" t="s" s="2">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="s" s="2">
+        <v>2500</v>
+      </c>
+      <c r="B1238" t="s" s="2">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="s" s="2">
+        <v>2502</v>
+      </c>
+      <c r="B1239" t="s" s="2">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="s" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B1240" t="s" s="2">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="s" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B1241" t="s" s="2">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="s" s="2">
+        <v>2508</v>
+      </c>
+      <c r="B1242" t="s" s="2">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="s" s="2">
+        <v>2510</v>
+      </c>
+      <c r="B1243" t="s" s="2">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="s" s="2">
+        <v>2512</v>
+      </c>
+      <c r="B1244" t="s" s="2">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="s" s="2">
+        <v>2514</v>
+      </c>
+      <c r="B1245" t="s" s="2">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="s" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B1246" t="s" s="2">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="s" s="2">
+        <v>2518</v>
+      </c>
+      <c r="B1247" t="s" s="2">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="s" s="2">
+        <v>2520</v>
+      </c>
+      <c r="B1248" t="s" s="2">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="s" s="2">
+        <v>2522</v>
+      </c>
+      <c r="B1249" t="s" s="2">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="s" s="2">
+        <v>2524</v>
+      </c>
+      <c r="B1250" t="s" s="2">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="s" s="2">
+        <v>2525</v>
+      </c>
+      <c r="B1251" t="s" s="2">
+        <v>2526</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="2527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="2559">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1842,7 +1842,7 @@
     <t>0538</t>
   </si>
   <si>
-    <t>Thérapie de groupe ou atelier à médiation orale et-ou écrite (groupe de parole, d'écriture)</t>
+    <t>Thérapie de groupe ou atelier à médiation orale et/ou écrite (groupe de parole, d'écriture)</t>
   </si>
   <si>
     <t>0539</t>
@@ -4134,7 +4134,7 @@
     <t>1014</t>
   </si>
   <si>
-    <t>Fourniture de matériel d'hygiène, de prévention et de RdRD</t>
+    <t>Fourniture de matériel d’hygiène, de prévention et de Réduction des Risques et des Dommages (RdRD)</t>
   </si>
   <si>
     <t>1015</t>
@@ -6624,7 +6624,7 @@
     <t>1453</t>
   </si>
   <si>
-    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
+    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
   </si>
   <si>
     <t>1454</t>
@@ -7386,205 +7386,301 @@
     <t>1582</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en cardiologie</t>
+    <t>Prise en charge spécialisée et continue en cardiologie</t>
   </si>
   <si>
     <t>1583</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie cardiaque et gros vaisseaux</t>
+    <t>Prise en charge spécialisée et continue en chirurgie cardiaque et gros vaisseaux</t>
   </si>
   <si>
     <t>1584</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie digestive et viscérale</t>
+    <t>Prise en charge spécialisée et continue en chirurgie digestive et viscérale</t>
   </si>
   <si>
     <t>1585</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie maxillo-faciale et stomatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie maxillo-faciale et stomatologie</t>
   </si>
   <si>
     <t>1586</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1587</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1588</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique viscérale et digestive</t>
+    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique viscérale et digestive</t>
   </si>
   <si>
     <t>1589</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie thoracique et pulmonaire</t>
+    <t>Prise en charge spécialisée et continue en chirurgie thoracique et pulmonaire</t>
   </si>
   <si>
     <t>1590</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie vasculaire</t>
+    <t>Prise en charge spécialisée et continue en chirurgie vasculaire</t>
   </si>
   <si>
     <t>1591</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en dermatologie</t>
+    <t>Prise en charge spécialisée et continue en dermatologie</t>
   </si>
   <si>
     <t>1592</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en endocrinologie</t>
+    <t>Prise en charge spécialisée et continue en endocrinologie</t>
   </si>
   <si>
     <t>1593</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gériatrie (gérontologie)</t>
+    <t>Prise en charge spécialisée et continue en gériatrie (gérontologie)</t>
   </si>
   <si>
     <t>1594</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gynécologie</t>
+    <t>Prise en charge spécialisée et continue en gynécologie</t>
   </si>
   <si>
     <t>1595</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hématologie</t>
+    <t>Prise en charge spécialisée et continue en hématologie</t>
   </si>
   <si>
     <t>1596</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hépato-gastro-entérologie</t>
+    <t>Prise en charge spécialisée et continue en hépato-gastro-entérologie</t>
   </si>
   <si>
     <t>1597</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en maladies infectieuses et tropicales</t>
+    <t>Prise en charge spécialisée et continue en maladies infectieuses et tropicales</t>
   </si>
   <si>
     <t>1598</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine interne</t>
+    <t>Prise en charge spécialisée et continue en médecine interne</t>
   </si>
   <si>
     <t>1599</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine vasculaire</t>
+    <t>Prise en charge spécialisée et continue en médecine vasculaire</t>
   </si>
   <si>
     <t>1600</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en néphrologie (dont dialyse)</t>
+    <t>Prise en charge spécialisée et continue en néphrologie (dont dialyse)</t>
   </si>
   <si>
     <t>1601</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurochirurgie</t>
+    <t>Prise en charge spécialisée et continue en neurochirurgie</t>
   </si>
   <si>
     <t>1602</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurologie</t>
+    <t>Prise en charge spécialisée et continue en neurologie</t>
   </si>
   <si>
     <t>1603</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oncologie</t>
+    <t>Prise en charge spécialisée et continue en oncologie</t>
   </si>
   <si>
     <t>1604</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en ophtalmologie</t>
+    <t>Prise en charge spécialisée et continue en ophtalmologie</t>
   </si>
   <si>
     <t>1605</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
+    <t>Prise en charge spécialisée et continue en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
   </si>
   <si>
     <t>1606</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pédiatrie</t>
+    <t>Prise en charge spécialisée et continue en pédiatrie</t>
   </si>
   <si>
     <t>1607</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pneumologie</t>
+    <t>Prise en charge spécialisée et continue en pneumologie</t>
   </si>
   <si>
     <t>1608</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en rhumatologie</t>
+    <t>Prise en charge spécialisée et continue en rhumatologie</t>
   </si>
   <si>
     <t>1609</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en urologie</t>
+    <t>Prise en charge spécialisée et continue en urologie</t>
   </si>
   <si>
     <t>1610</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en caisson oxygène hyperbare</t>
+    <t>Prise en charge spécialisée et continue en caisson oxygène hyperbare</t>
   </si>
   <si>
     <t>1611</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie de la main SOS main</t>
+    <t>Prise en charge spécialisée et continue en chirurgie de la main SOS main</t>
   </si>
   <si>
     <t>1612</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en odontologie</t>
+    <t>Prise en charge spécialisée et continue en odontologie</t>
   </si>
   <si>
     <t>1613</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en psychiatrie (dont équipe de liaison)</t>
+    <t>Prise en charge spécialisée et continue en psychiatrie (dont équipe de liaison)</t>
   </si>
   <si>
     <t>1614</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en radiologie interventionnelle</t>
+    <t>Prise en charge spécialisée et continue en radiologie interventionnelle</t>
   </si>
   <si>
     <t>1615</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) rachis</t>
+    <t>Prise en charge spécialisée et continue rachis</t>
+  </si>
+  <si>
+    <t>1616</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée du pied diabétique de grade 2 et 3</t>
+  </si>
+  <si>
+    <t>1617</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée soins de support oncologie</t>
+  </si>
+  <si>
+    <t>1618</t>
+  </si>
+  <si>
+    <t>Orthoplastie (appareillage d’orteil)</t>
+  </si>
+  <si>
+    <t>1619</t>
+  </si>
+  <si>
+    <t>Orthonyxie (appareillage d’ongle)</t>
+  </si>
+  <si>
+    <t>1620</t>
+  </si>
+  <si>
+    <t>Onychoplastie (reconstruction de l’ongle)</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>Orthèse plantaire (semelle orthopédique)</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>Bilan diagnostique podologique de la prévention de la chute</t>
+  </si>
+  <si>
+    <t>1623</t>
+  </si>
+  <si>
+    <t>Rééducation du pied (sous la cheville)</t>
+  </si>
+  <si>
+    <t>1624</t>
+  </si>
+  <si>
+    <t>Contention nocturne</t>
+  </si>
+  <si>
+    <t>1625</t>
+  </si>
+  <si>
+    <t>Soin de pédicurie</t>
+  </si>
+  <si>
+    <t>1626</t>
+  </si>
+  <si>
+    <t>Traitement de la verrue plantaire par azote liquide</t>
+  </si>
+  <si>
+    <t>1627</t>
+  </si>
+  <si>
+    <t>Traitement sans douleur de l’ongle incarné par phénolisation (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1628</t>
+  </si>
+  <si>
+    <t>Prélèvement unguéal pour analyse biologique (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1629</t>
+  </si>
+  <si>
+    <t>Confection de semelle de comblement en polyuréthane (PU) pour amputation partielle du pied</t>
+  </si>
+  <si>
+    <t>1630</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et continue en pédopsychiatrie (dont équipe de liaison)</t>
+  </si>
+  <si>
+    <t>1631</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et continue SOS main</t>
   </si>
   <si>
     <t/>
@@ -7855,7 +7951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1251"/>
+  <dimension ref="A1:B1267"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -17859,15 +17955,143 @@
         <v>2524</v>
       </c>
       <c r="B1250" t="s" s="2">
-        <v>2524</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="s" s="2">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="B1251" t="s" s="2">
-        <v>2526</v>
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="s" s="2">
+        <v>2528</v>
+      </c>
+      <c r="B1252" t="s" s="2">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="s" s="2">
+        <v>2530</v>
+      </c>
+      <c r="B1253" t="s" s="2">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="s" s="2">
+        <v>2532</v>
+      </c>
+      <c r="B1254" t="s" s="2">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="s" s="2">
+        <v>2534</v>
+      </c>
+      <c r="B1255" t="s" s="2">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="s" s="2">
+        <v>2536</v>
+      </c>
+      <c r="B1256" t="s" s="2">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="s" s="2">
+        <v>2538</v>
+      </c>
+      <c r="B1257" t="s" s="2">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="s" s="2">
+        <v>2540</v>
+      </c>
+      <c r="B1258" t="s" s="2">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="s" s="2">
+        <v>2542</v>
+      </c>
+      <c r="B1259" t="s" s="2">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="s" s="2">
+        <v>2544</v>
+      </c>
+      <c r="B1260" t="s" s="2">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="s" s="2">
+        <v>2546</v>
+      </c>
+      <c r="B1261" t="s" s="2">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="s" s="2">
+        <v>2548</v>
+      </c>
+      <c r="B1262" t="s" s="2">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="s" s="2">
+        <v>2550</v>
+      </c>
+      <c r="B1263" t="s" s="2">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="s" s="2">
+        <v>2552</v>
+      </c>
+      <c r="B1264" t="s" s="2">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="s" s="2">
+        <v>2554</v>
+      </c>
+      <c r="B1265" t="s" s="2">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="s" s="2">
+        <v>2556</v>
+      </c>
+      <c r="B1266" t="s" s="2">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="s" s="2">
+        <v>2557</v>
+      </c>
+      <c r="B1267" t="s" s="2">
+        <v>2558</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="2559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2643" uniqueCount="2641">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260601120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -714,7 +714,7 @@
     <t>0182</t>
   </si>
   <si>
-    <t>Education thérapeutique labellisée du patient asthmatique (école de l'asthme)</t>
+    <t>Programme d’ETP labellisée - Asthme</t>
   </si>
   <si>
     <t>0183</t>
@@ -1842,7 +1842,7 @@
     <t>0538</t>
   </si>
   <si>
-    <t>Thérapie de groupe ou atelier à médiation orale et/ou écrite (groupe de parole, d'écriture)</t>
+    <t>Thérapie de groupe ou atelier à médiation orale et-ou écrite (groupe de parole, d'écriture)</t>
   </si>
   <si>
     <t>0539</t>
@@ -4134,7 +4134,7 @@
     <t>1014</t>
   </si>
   <si>
-    <t>Fourniture de matériel d’hygiène, de prévention et de Réduction des Risques et des Dommages (RdRD)</t>
+    <t>Fourniture de matériel d'hygiène, de prévention et de RdRD</t>
   </si>
   <si>
     <t>1015</t>
@@ -5694,13 +5694,13 @@
     <t>1281</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Affections neurologiques</t>
+    <t>Programme d'ETP labellisée - Affections neurologiques (hors AVC)</t>
   </si>
   <si>
     <t>1282</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Diabète et pathologies endocrines</t>
+    <t>Programme d'ETP labellisée - Diabète</t>
   </si>
   <si>
     <t>1283</t>
@@ -5724,7 +5724,7 @@
     <t>1286</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Maladies Cancéreuses</t>
+    <t>Programme d'ETP labellisée - Maladies Cancéreuses (dont soins de support)</t>
   </si>
   <si>
     <t>1287</t>
@@ -5742,13 +5742,13 @@
     <t>1289</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Maladies du système ostéoarticulaire</t>
+    <t>Programme d'ETP labellisée - Maladies rhumatologiques et du système ostéoarticulaire</t>
   </si>
   <si>
     <t>1290</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Maladies infectieuses</t>
+    <t>Programme d'ETP labellisée - Maladies infectieuses chroniques (dont VIH et tuberculose)</t>
   </si>
   <si>
     <t>1291</t>
@@ -6594,7 +6594,7 @@
     <t>1447</t>
   </si>
   <si>
-    <t>Prescription de vaccination</t>
+    <t>Prescription de vaccin</t>
   </si>
   <si>
     <t>1448</t>
@@ -6624,7 +6624,7 @@
     <t>1453</t>
   </si>
   <si>
-    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
+    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
   </si>
   <si>
     <t>1454</t>
@@ -7362,7 +7362,7 @@
     <t>1578</t>
   </si>
   <si>
-    <t>Centre expert Parkinson</t>
+    <t>Centre expert en maladie de Parkinson</t>
   </si>
   <si>
     <t>1579</t>
@@ -7386,301 +7386,547 @@
     <t>1582</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en cardiologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en cardiologie</t>
   </si>
   <si>
     <t>1583</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie cardiaque et gros vaisseaux</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie cardiaque et gros vaisseaux</t>
   </si>
   <si>
     <t>1584</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie digestive et viscérale</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie digestive et viscérale</t>
   </si>
   <si>
     <t>1585</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie maxillo-faciale et stomatologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie maxillo-faciale et stomatologie</t>
   </si>
   <si>
     <t>1586</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1587</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1588</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique viscérale et digestive</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique viscérale et digestive</t>
   </si>
   <si>
     <t>1589</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie thoracique et pulmonaire</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie thoracique et pulmonaire</t>
   </si>
   <si>
     <t>1590</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie vasculaire</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie vasculaire</t>
   </si>
   <si>
     <t>1591</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en dermatologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en dermatologie</t>
   </si>
   <si>
     <t>1592</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en endocrinologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en endocrinologie</t>
   </si>
   <si>
     <t>1593</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en gériatrie (gérontologie)</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gériatrie (gérontologie)</t>
   </si>
   <si>
     <t>1594</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en gynécologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gynécologie</t>
   </si>
   <si>
     <t>1595</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en hématologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hématologie</t>
   </si>
   <si>
     <t>1596</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en hépato-gastro-entérologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hépato-gastro-entérologie</t>
   </si>
   <si>
     <t>1597</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en maladies infectieuses et tropicales</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en maladies infectieuses et tropicales</t>
   </si>
   <si>
     <t>1598</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en médecine interne</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine interne</t>
   </si>
   <si>
     <t>1599</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en médecine vasculaire</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine vasculaire</t>
   </si>
   <si>
     <t>1600</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en néphrologie (dont dialyse)</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en néphrologie (dont dialyse)</t>
   </si>
   <si>
     <t>1601</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en neurochirurgie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurochirurgie</t>
   </si>
   <si>
     <t>1602</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en neurologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurologie</t>
   </si>
   <si>
     <t>1603</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en oncologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oncologie</t>
   </si>
   <si>
     <t>1604</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en ophtalmologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en ophtalmologie</t>
   </si>
   <si>
     <t>1605</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
   </si>
   <si>
     <t>1606</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en pédiatrie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pédiatrie</t>
   </si>
   <si>
     <t>1607</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en pneumologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pneumologie</t>
   </si>
   <si>
     <t>1608</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en rhumatologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en rhumatologie</t>
   </si>
   <si>
     <t>1609</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en urologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en urologie</t>
   </si>
   <si>
     <t>1610</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en caisson oxygène hyperbare</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en caisson oxygène hyperbare</t>
   </si>
   <si>
     <t>1611</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en chirurgie de la main SOS main</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie de la main SOS main</t>
   </si>
   <si>
     <t>1612</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en odontologie</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en odontologie</t>
   </si>
   <si>
     <t>1613</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en psychiatrie (dont équipe de liaison)</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en psychiatrie (dont équipe de liaison)</t>
   </si>
   <si>
     <t>1614</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue en radiologie interventionnelle</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en radiologie interventionnelle</t>
   </si>
   <si>
     <t>1615</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et continue rachis</t>
-  </si>
-  <si>
-    <t>1616</t>
-  </si>
-  <si>
-    <t>Pédicurie-podologie conventionnée du pied diabétique de grade 2 et 3</t>
-  </si>
-  <si>
-    <t>1617</t>
-  </si>
-  <si>
-    <t>Pédicurie-podologie conventionnée soins de support oncologie</t>
-  </si>
-  <si>
-    <t>1618</t>
-  </si>
-  <si>
-    <t>Orthoplastie (appareillage d’orteil)</t>
-  </si>
-  <si>
-    <t>1619</t>
-  </si>
-  <si>
-    <t>Orthonyxie (appareillage d’ongle)</t>
-  </si>
-  <si>
-    <t>1620</t>
-  </si>
-  <si>
-    <t>Onychoplastie (reconstruction de l’ongle)</t>
-  </si>
-  <si>
-    <t>1621</t>
-  </si>
-  <si>
-    <t>Orthèse plantaire (semelle orthopédique)</t>
-  </si>
-  <si>
-    <t>1622</t>
-  </si>
-  <si>
-    <t>Bilan diagnostique podologique de la prévention de la chute</t>
-  </si>
-  <si>
-    <t>1623</t>
-  </si>
-  <si>
-    <t>Rééducation du pied (sous la cheville)</t>
-  </si>
-  <si>
-    <t>1624</t>
-  </si>
-  <si>
-    <t>Contention nocturne</t>
-  </si>
-  <si>
-    <t>1625</t>
-  </si>
-  <si>
-    <t>Soin de pédicurie</t>
-  </si>
-  <si>
-    <t>1626</t>
-  </si>
-  <si>
-    <t>Traitement de la verrue plantaire par azote liquide</t>
-  </si>
-  <si>
-    <t>1627</t>
-  </si>
-  <si>
-    <t>Traitement sans douleur de l’ongle incarné par phénolisation (protocole de coopération)</t>
-  </si>
-  <si>
-    <t>1628</t>
-  </si>
-  <si>
-    <t>Prélèvement unguéal pour analyse biologique (protocole de coopération)</t>
-  </si>
-  <si>
-    <t>1629</t>
-  </si>
-  <si>
-    <t>Confection de semelle de comblement en polyuréthane (PU) pour amputation partielle du pied</t>
-  </si>
-  <si>
-    <t>1630</t>
-  </si>
-  <si>
-    <t>Prise en charge spécialisée et continue en pédopsychiatrie (dont équipe de liaison)</t>
-  </si>
-  <si>
-    <t>1631</t>
-  </si>
-  <si>
-    <t>Prise en charge spécialisée et continue SOS main</t>
+    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) rachis</t>
+  </si>
+  <si>
+    <t>1632</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Accident Vasculaire Cérébral (AVC)</t>
+  </si>
+  <si>
+    <t>1633</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Allergologie</t>
+  </si>
+  <si>
+    <t>1634</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Anticoagulants oraux (AVK, AOD, HBPM)</t>
+  </si>
+  <si>
+    <t>1635</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Maladies rares (dont maladies du sang, drépanocytose, amylose)</t>
+  </si>
+  <si>
+    <t>1636</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Maladies urologiques et gynécologiques</t>
+  </si>
+  <si>
+    <t>1637</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Obésité</t>
+  </si>
+  <si>
+    <t>1638</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Ophtalmologie</t>
+  </si>
+  <si>
+    <t>1639</t>
+  </si>
+  <si>
+    <t>Programme d’ETP labellisée - Pathologies endocrines (hors diabète, hors obésité)</t>
+  </si>
+  <si>
+    <t>1640</t>
+  </si>
+  <si>
+    <t>Lyophilisation de lait maternel</t>
+  </si>
+  <si>
+    <t>1641</t>
+  </si>
+  <si>
+    <t>Centre de Traitement des Brûlés (CTB)</t>
+  </si>
+  <si>
+    <t>1642</t>
+  </si>
+  <si>
+    <t>Remédiation psychosociale</t>
+  </si>
+  <si>
+    <t>1643</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice d’un trouble du neurodéveloppement</t>
+  </si>
+  <si>
+    <t>1644</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice d’un trouble de l’apprentissage</t>
+  </si>
+  <si>
+    <t>1645</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice des troubles tonico-émotionnels</t>
+  </si>
+  <si>
+    <t>1646</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice des troubles de la latéralisation</t>
+  </si>
+  <si>
+    <t>1647</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice du schéma corporel et des représentations du corps</t>
+  </si>
+  <si>
+    <t>1648</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice des troubles d’organisation spatio-temporelle</t>
+  </si>
+  <si>
+    <t>1649</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice des troubles sensoriels</t>
+  </si>
+  <si>
+    <t>1650</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice du développement psychomoteur</t>
+  </si>
+  <si>
+    <t>1651</t>
+  </si>
+  <si>
+    <t>Réadaptation psychomotrice des troubles psychiques</t>
+  </si>
+  <si>
+    <t>1652</t>
+  </si>
+  <si>
+    <t>Programmes d’Entraînement aux Habiletés Parentales</t>
+  </si>
+  <si>
+    <t>1653</t>
+  </si>
+  <si>
+    <t>Relaxation psychomotrice</t>
+  </si>
+  <si>
+    <t>1654</t>
+  </si>
+  <si>
+    <t>Evaluation et/ou prise en soins orthoptiques à visée visio-vestibulaire dans le cadre des troubles de l'équilibration et vertiges</t>
+  </si>
+  <si>
+    <t>1655</t>
+  </si>
+  <si>
+    <t>Evaluation visuelle des troubles orthoptiques et neurovisuels dans le cadre des troubles du neuro-développement (TNV - TND)</t>
+  </si>
+  <si>
+    <t>1656</t>
+  </si>
+  <si>
+    <t>Bilan de dépistage réfractif et de l'amblyopie</t>
+  </si>
+  <si>
+    <t>1657</t>
+  </si>
+  <si>
+    <t>Bilan visuel dans le cadre d'un renouvellement ou d'une adaptation de la correction optique (Protocole de coopération Renouvellement d'Optique (RNO))</t>
+  </si>
+  <si>
+    <t>1658</t>
+  </si>
+  <si>
+    <t>Exploration du sens chromatique</t>
+  </si>
+  <si>
+    <t>1659</t>
+  </si>
+  <si>
+    <t>Examen de la courbe d'adaptation à l'obscurité</t>
+  </si>
+  <si>
+    <t>1660</t>
+  </si>
+  <si>
+    <t>Protocole de dépistage de la rétinopathie diabétique</t>
+  </si>
+  <si>
+    <t>1661</t>
+  </si>
+  <si>
+    <t>Examen dépistage réfractif avec Photoscreener</t>
+  </si>
+  <si>
+    <t>1662</t>
+  </si>
+  <si>
+    <t>Bilan visuel primo-prescription ou renouvellement de la correction optique (lunettes, lentilles, souples) pour les patients de 16 ans à 42 ans</t>
+  </si>
+  <si>
+    <t>1663</t>
+  </si>
+  <si>
+    <t>Evaluation oculométrique par enregistrement – technique d'Eye tracking</t>
+  </si>
+  <si>
+    <t>1664</t>
+  </si>
+  <si>
+    <t>Evaluation et/ou prise en soins dans le cadre de particularités sensorielles et perceptives (profil sensoriel de DUNN, BOGDASHINA)</t>
+  </si>
+  <si>
+    <t>1665</t>
+  </si>
+  <si>
+    <t>Evaluation orthoptique et/ou prise en soins avec ajustement d'aide optique et nouvelle technologie associé à un handicap de la fonction visuelle (RV)</t>
+  </si>
+  <si>
+    <t>1666</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi dans le cadre de l'adaptation du logement lors d'un handicap de la fonction visuelle</t>
+  </si>
+  <si>
+    <t>1667</t>
+  </si>
+  <si>
+    <t>Evaluation orthoptique de la fonction visuelle et/ou prise en soins dans le cadre de la conduite automobile</t>
+  </si>
+  <si>
+    <t>1668</t>
+  </si>
+  <si>
+    <t>Evaluation orthoptique de la fonction visuelle et/ou prise en soins dans le cadre de l'activité physique adaptée</t>
+  </si>
+  <si>
+    <t>1669</t>
+  </si>
+  <si>
+    <t>Evaluation et/ou prise en soins orthoptiques neurovisuels des troubles de la cognition visuelle</t>
+  </si>
+  <si>
+    <t>1670</t>
+  </si>
+  <si>
+    <t>Evaluation et/ou prise en soins de la rééducation neurovisuelle visuo-vestibulaire (vertiges)</t>
+  </si>
+  <si>
+    <t>1671</t>
+  </si>
+  <si>
+    <t>Dispensation médicamenteuse à domicile en cas d’impossibilité du patient à se déplacer</t>
+  </si>
+  <si>
+    <t>1672</t>
+  </si>
+  <si>
+    <t>Préparation des doses à administrer (PDA)</t>
+  </si>
+  <si>
+    <t>1673</t>
+  </si>
+  <si>
+    <t>Entretien pharmaceutique de la femme enceinte</t>
+  </si>
+  <si>
+    <t>1674</t>
+  </si>
+  <si>
+    <t>Entretien pharmaceutique du patient asthmatique sous corticostéroïdes inhalés (CSI)</t>
+  </si>
+  <si>
+    <t>1675</t>
+  </si>
+  <si>
+    <t>Entretien pharmaceutique du patient sous anticoagulant oral (AOD/AVK)</t>
+  </si>
+  <si>
+    <t>1676</t>
+  </si>
+  <si>
+    <t>Entretien pharmaceutique du patient sous anticancéreux oraux</t>
+  </si>
+  <si>
+    <t>1677</t>
+  </si>
+  <si>
+    <t>Entretien pharmaceutique du patient sous antalgique opioïde de pallier 2</t>
+  </si>
+  <si>
+    <t>1678</t>
+  </si>
+  <si>
+    <t>Entretien bilan partagé de médication</t>
+  </si>
+  <si>
+    <t>1679</t>
+  </si>
+  <si>
+    <t>Réseau France Santé</t>
+  </si>
+  <si>
+    <t>1680</t>
+  </si>
+  <si>
+    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
+  </si>
+  <si>
+    <t>1681</t>
+  </si>
+  <si>
+    <t>Orthèses et prothèses externes (orthopédie sur mesure)</t>
+  </si>
+  <si>
+    <t>1682</t>
+  </si>
+  <si>
+    <t>Orthèses et prothèses externes (de série)</t>
+  </si>
+  <si>
+    <t>1683</t>
+  </si>
+  <si>
+    <t>Optique lunetterie</t>
+  </si>
+  <si>
+    <t>1684</t>
+  </si>
+  <si>
+    <t>Audioprothèse</t>
+  </si>
+  <si>
+    <t>1685</t>
+  </si>
+  <si>
+    <t>Prise en charge de l’éruption cutanée vésiculeuse prurigineuse chez l’enfant (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1686</t>
+  </si>
+  <si>
+    <t>Renouvellement du traitement de la rhino-conjonctivite allergique saisonnière (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1687</t>
+  </si>
+  <si>
+    <t>Distribution de comprimés d’iode en application du Plan Particulier d’Intervention (PPI)</t>
+  </si>
+  <si>
+    <t>1688</t>
+  </si>
+  <si>
+    <t>Remise du kit de dépistage du cancer colorectal</t>
   </si>
   <si>
     <t/>
@@ -7951,7 +8197,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1267"/>
+  <dimension ref="A1:B1308"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -18083,15 +18329,343 @@
         <v>2556</v>
       </c>
       <c r="B1266" t="s" s="2">
-        <v>2556</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="s" s="2">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="B1267" t="s" s="2">
-        <v>2558</v>
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="s" s="2">
+        <v>2560</v>
+      </c>
+      <c r="B1268" t="s" s="2">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="s" s="2">
+        <v>2562</v>
+      </c>
+      <c r="B1269" t="s" s="2">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="s" s="2">
+        <v>2564</v>
+      </c>
+      <c r="B1270" t="s" s="2">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="s" s="2">
+        <v>2566</v>
+      </c>
+      <c r="B1271" t="s" s="2">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="s" s="2">
+        <v>2568</v>
+      </c>
+      <c r="B1272" t="s" s="2">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="s" s="2">
+        <v>2570</v>
+      </c>
+      <c r="B1273" t="s" s="2">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="s" s="2">
+        <v>2572</v>
+      </c>
+      <c r="B1274" t="s" s="2">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="s" s="2">
+        <v>2574</v>
+      </c>
+      <c r="B1275" t="s" s="2">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="s" s="2">
+        <v>2576</v>
+      </c>
+      <c r="B1276" t="s" s="2">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="s" s="2">
+        <v>2578</v>
+      </c>
+      <c r="B1277" t="s" s="2">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="s" s="2">
+        <v>2580</v>
+      </c>
+      <c r="B1278" t="s" s="2">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="s" s="2">
+        <v>2582</v>
+      </c>
+      <c r="B1279" t="s" s="2">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="s" s="2">
+        <v>2584</v>
+      </c>
+      <c r="B1280" t="s" s="2">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="s" s="2">
+        <v>2586</v>
+      </c>
+      <c r="B1281" t="s" s="2">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="s" s="2">
+        <v>2588</v>
+      </c>
+      <c r="B1282" t="s" s="2">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="s" s="2">
+        <v>2590</v>
+      </c>
+      <c r="B1283" t="s" s="2">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="s" s="2">
+        <v>2592</v>
+      </c>
+      <c r="B1284" t="s" s="2">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="s" s="2">
+        <v>2594</v>
+      </c>
+      <c r="B1285" t="s" s="2">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="s" s="2">
+        <v>2596</v>
+      </c>
+      <c r="B1286" t="s" s="2">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="s" s="2">
+        <v>2598</v>
+      </c>
+      <c r="B1287" t="s" s="2">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="s" s="2">
+        <v>2600</v>
+      </c>
+      <c r="B1288" t="s" s="2">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="s" s="2">
+        <v>2602</v>
+      </c>
+      <c r="B1289" t="s" s="2">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="s" s="2">
+        <v>2604</v>
+      </c>
+      <c r="B1290" t="s" s="2">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="s" s="2">
+        <v>2606</v>
+      </c>
+      <c r="B1291" t="s" s="2">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="s" s="2">
+        <v>2608</v>
+      </c>
+      <c r="B1292" t="s" s="2">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="s" s="2">
+        <v>2610</v>
+      </c>
+      <c r="B1293" t="s" s="2">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="s" s="2">
+        <v>2612</v>
+      </c>
+      <c r="B1294" t="s" s="2">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="s" s="2">
+        <v>2614</v>
+      </c>
+      <c r="B1295" t="s" s="2">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="s" s="2">
+        <v>2616</v>
+      </c>
+      <c r="B1296" t="s" s="2">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="s" s="2">
+        <v>2618</v>
+      </c>
+      <c r="B1297" t="s" s="2">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="s" s="2">
+        <v>2620</v>
+      </c>
+      <c r="B1298" t="s" s="2">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="s" s="2">
+        <v>2622</v>
+      </c>
+      <c r="B1299" t="s" s="2">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="s" s="2">
+        <v>2624</v>
+      </c>
+      <c r="B1300" t="s" s="2">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="s" s="2">
+        <v>2626</v>
+      </c>
+      <c r="B1301" t="s" s="2">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="s" s="2">
+        <v>2628</v>
+      </c>
+      <c r="B1302" t="s" s="2">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="s" s="2">
+        <v>2630</v>
+      </c>
+      <c r="B1303" t="s" s="2">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="s" s="2">
+        <v>2632</v>
+      </c>
+      <c r="B1304" t="s" s="2">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="s" s="2">
+        <v>2634</v>
+      </c>
+      <c r="B1305" t="s" s="2">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="s" s="2">
+        <v>2636</v>
+      </c>
+      <c r="B1306" t="s" s="2">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="s" s="2">
+        <v>2638</v>
+      </c>
+      <c r="B1307" t="s" s="2">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="s" s="2">
+        <v>2639</v>
+      </c>
+      <c r="B1308" t="s" s="2">
+        <v>2640</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2643" uniqueCount="2641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="2559">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -714,7 +714,7 @@
     <t>0182</t>
   </si>
   <si>
-    <t>Programme d’ETP labellisée - Asthme</t>
+    <t>Education thérapeutique labellisée du patient asthmatique (école de l'asthme)</t>
   </si>
   <si>
     <t>0183</t>
@@ -1842,7 +1842,7 @@
     <t>0538</t>
   </si>
   <si>
-    <t>Thérapie de groupe ou atelier à médiation orale et-ou écrite (groupe de parole, d'écriture)</t>
+    <t>Thérapie de groupe ou atelier à médiation orale et/ou écrite (groupe de parole, d'écriture)</t>
   </si>
   <si>
     <t>0539</t>
@@ -4134,7 +4134,7 @@
     <t>1014</t>
   </si>
   <si>
-    <t>Fourniture de matériel d'hygiène, de prévention et de RdRD</t>
+    <t>Fourniture de matériel d’hygiène, de prévention et de Réduction des Risques et des Dommages (RdRD)</t>
   </si>
   <si>
     <t>1015</t>
@@ -5694,13 +5694,13 @@
     <t>1281</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Affections neurologiques (hors AVC)</t>
+    <t>Programme d'ETP labellisée - Affections neurologiques</t>
   </si>
   <si>
     <t>1282</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Diabète</t>
+    <t>Programme d'ETP labellisée - Diabète et pathologies endocrines</t>
   </si>
   <si>
     <t>1283</t>
@@ -5724,7 +5724,7 @@
     <t>1286</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Maladies Cancéreuses (dont soins de support)</t>
+    <t>Programme d'ETP labellisée - Maladies Cancéreuses</t>
   </si>
   <si>
     <t>1287</t>
@@ -5742,13 +5742,13 @@
     <t>1289</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Maladies rhumatologiques et du système ostéoarticulaire</t>
+    <t>Programme d'ETP labellisée - Maladies du système ostéoarticulaire</t>
   </si>
   <si>
     <t>1290</t>
   </si>
   <si>
-    <t>Programme d'ETP labellisée - Maladies infectieuses chroniques (dont VIH et tuberculose)</t>
+    <t>Programme d'ETP labellisée - Maladies infectieuses</t>
   </si>
   <si>
     <t>1291</t>
@@ -6594,7 +6594,7 @@
     <t>1447</t>
   </si>
   <si>
-    <t>Prescription de vaccin</t>
+    <t>Prescription de vaccination</t>
   </si>
   <si>
     <t>1448</t>
@@ -6624,7 +6624,7 @@
     <t>1453</t>
   </si>
   <si>
-    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
+    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
   </si>
   <si>
     <t>1454</t>
@@ -7362,7 +7362,7 @@
     <t>1578</t>
   </si>
   <si>
-    <t>Centre expert en maladie de Parkinson</t>
+    <t>Centre expert Parkinson</t>
   </si>
   <si>
     <t>1579</t>
@@ -7386,547 +7386,301 @@
     <t>1582</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en cardiologie</t>
+    <t>Prise en charge spécialisée et continue en cardiologie</t>
   </si>
   <si>
     <t>1583</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie cardiaque et gros vaisseaux</t>
+    <t>Prise en charge spécialisée et continue en chirurgie cardiaque et gros vaisseaux</t>
   </si>
   <si>
     <t>1584</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie digestive et viscérale</t>
+    <t>Prise en charge spécialisée et continue en chirurgie digestive et viscérale</t>
   </si>
   <si>
     <t>1585</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie maxillo-faciale et stomatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie maxillo-faciale et stomatologie</t>
   </si>
   <si>
     <t>1586</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1587</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1588</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique viscérale et digestive</t>
+    <t>Prise en charge spécialisée et continue en chirurgie pédiatrique viscérale et digestive</t>
   </si>
   <si>
     <t>1589</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie thoracique et pulmonaire</t>
+    <t>Prise en charge spécialisée et continue en chirurgie thoracique et pulmonaire</t>
   </si>
   <si>
     <t>1590</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie vasculaire</t>
+    <t>Prise en charge spécialisée et continue en chirurgie vasculaire</t>
   </si>
   <si>
     <t>1591</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en dermatologie</t>
+    <t>Prise en charge spécialisée et continue en dermatologie</t>
   </si>
   <si>
     <t>1592</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en endocrinologie</t>
+    <t>Prise en charge spécialisée et continue en endocrinologie</t>
   </si>
   <si>
     <t>1593</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gériatrie (gérontologie)</t>
+    <t>Prise en charge spécialisée et continue en gériatrie (gérontologie)</t>
   </si>
   <si>
     <t>1594</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gynécologie</t>
+    <t>Prise en charge spécialisée et continue en gynécologie</t>
   </si>
   <si>
     <t>1595</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hématologie</t>
+    <t>Prise en charge spécialisée et continue en hématologie</t>
   </si>
   <si>
     <t>1596</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hépato-gastro-entérologie</t>
+    <t>Prise en charge spécialisée et continue en hépato-gastro-entérologie</t>
   </si>
   <si>
     <t>1597</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en maladies infectieuses et tropicales</t>
+    <t>Prise en charge spécialisée et continue en maladies infectieuses et tropicales</t>
   </si>
   <si>
     <t>1598</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine interne</t>
+    <t>Prise en charge spécialisée et continue en médecine interne</t>
   </si>
   <si>
     <t>1599</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine vasculaire</t>
+    <t>Prise en charge spécialisée et continue en médecine vasculaire</t>
   </si>
   <si>
     <t>1600</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en néphrologie (dont dialyse)</t>
+    <t>Prise en charge spécialisée et continue en néphrologie (dont dialyse)</t>
   </si>
   <si>
     <t>1601</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurochirurgie</t>
+    <t>Prise en charge spécialisée et continue en neurochirurgie</t>
   </si>
   <si>
     <t>1602</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurologie</t>
+    <t>Prise en charge spécialisée et continue en neurologie</t>
   </si>
   <si>
     <t>1603</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oncologie</t>
+    <t>Prise en charge spécialisée et continue en oncologie</t>
   </si>
   <si>
     <t>1604</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en ophtalmologie</t>
+    <t>Prise en charge spécialisée et continue en ophtalmologie</t>
   </si>
   <si>
     <t>1605</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
+    <t>Prise en charge spécialisée et continue en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
   </si>
   <si>
     <t>1606</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pédiatrie</t>
+    <t>Prise en charge spécialisée et continue en pédiatrie</t>
   </si>
   <si>
     <t>1607</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pneumologie</t>
+    <t>Prise en charge spécialisée et continue en pneumologie</t>
   </si>
   <si>
     <t>1608</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en rhumatologie</t>
+    <t>Prise en charge spécialisée et continue en rhumatologie</t>
   </si>
   <si>
     <t>1609</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en urologie</t>
+    <t>Prise en charge spécialisée et continue en urologie</t>
   </si>
   <si>
     <t>1610</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en caisson oxygène hyperbare</t>
+    <t>Prise en charge spécialisée et continue en caisson oxygène hyperbare</t>
   </si>
   <si>
     <t>1611</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie de la main SOS main</t>
+    <t>Prise en charge spécialisée et continue en chirurgie de la main SOS main</t>
   </si>
   <si>
     <t>1612</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en odontologie</t>
+    <t>Prise en charge spécialisée et continue en odontologie</t>
   </si>
   <si>
     <t>1613</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en psychiatrie (dont équipe de liaison)</t>
+    <t>Prise en charge spécialisée et continue en psychiatrie (dont équipe de liaison)</t>
   </si>
   <si>
     <t>1614</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en radiologie interventionnelle</t>
+    <t>Prise en charge spécialisée et continue en radiologie interventionnelle</t>
   </si>
   <si>
     <t>1615</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) rachis</t>
-  </si>
-  <si>
-    <t>1632</t>
-  </si>
-  <si>
-    <t>Programme d’ETP labellisée - Accident Vasculaire Cérébral (AVC)</t>
-  </si>
-  <si>
-    <t>1633</t>
-  </si>
-  <si>
-    <t>Programme d’ETP labellisée - Allergologie</t>
-  </si>
-  <si>
-    <t>1634</t>
-  </si>
-  <si>
-    <t>Programme d’ETP labellisée - Anticoagulants oraux (AVK, AOD, HBPM)</t>
-  </si>
-  <si>
-    <t>1635</t>
-  </si>
-  <si>
-    <t>Programme d’ETP labellisée - Maladies rares (dont maladies du sang, drépanocytose, amylose)</t>
-  </si>
-  <si>
-    <t>1636</t>
-  </si>
-  <si>
-    <t>Programme d’ETP labellisée - Maladies urologiques et gynécologiques</t>
-  </si>
-  <si>
-    <t>1637</t>
-  </si>
-  <si>
-    <t>Programme d’ETP labellisée - Obésité</t>
-  </si>
-  <si>
-    <t>1638</t>
-  </si>
-  <si>
-    <t>Programme d’ETP labellisée - Ophtalmologie</t>
-  </si>
-  <si>
-    <t>1639</t>
-  </si>
-  <si>
-    <t>Programme d’ETP labellisée - Pathologies endocrines (hors diabète, hors obésité)</t>
-  </si>
-  <si>
-    <t>1640</t>
-  </si>
-  <si>
-    <t>Lyophilisation de lait maternel</t>
-  </si>
-  <si>
-    <t>1641</t>
-  </si>
-  <si>
-    <t>Centre de Traitement des Brûlés (CTB)</t>
-  </si>
-  <si>
-    <t>1642</t>
-  </si>
-  <si>
-    <t>Remédiation psychosociale</t>
-  </si>
-  <si>
-    <t>1643</t>
-  </si>
-  <si>
-    <t>Réadaptation psychomotrice d’un trouble du neurodéveloppement</t>
-  </si>
-  <si>
-    <t>1644</t>
-  </si>
-  <si>
-    <t>Réadaptation psychomotrice d’un trouble de l’apprentissage</t>
-  </si>
-  <si>
-    <t>1645</t>
-  </si>
-  <si>
-    <t>Réadaptation psychomotrice des troubles tonico-émotionnels</t>
-  </si>
-  <si>
-    <t>1646</t>
-  </si>
-  <si>
-    <t>Réadaptation psychomotrice des troubles de la latéralisation</t>
-  </si>
-  <si>
-    <t>1647</t>
-  </si>
-  <si>
-    <t>Réadaptation psychomotrice du schéma corporel et des représentations du corps</t>
-  </si>
-  <si>
-    <t>1648</t>
-  </si>
-  <si>
-    <t>Réadaptation psychomotrice des troubles d’organisation spatio-temporelle</t>
-  </si>
-  <si>
-    <t>1649</t>
-  </si>
-  <si>
-    <t>Réadaptation psychomotrice des troubles sensoriels</t>
-  </si>
-  <si>
-    <t>1650</t>
-  </si>
-  <si>
-    <t>Réadaptation psychomotrice du développement psychomoteur</t>
-  </si>
-  <si>
-    <t>1651</t>
-  </si>
-  <si>
-    <t>Réadaptation psychomotrice des troubles psychiques</t>
-  </si>
-  <si>
-    <t>1652</t>
-  </si>
-  <si>
-    <t>Programmes d’Entraînement aux Habiletés Parentales</t>
-  </si>
-  <si>
-    <t>1653</t>
-  </si>
-  <si>
-    <t>Relaxation psychomotrice</t>
-  </si>
-  <si>
-    <t>1654</t>
-  </si>
-  <si>
-    <t>Evaluation et/ou prise en soins orthoptiques à visée visio-vestibulaire dans le cadre des troubles de l'équilibration et vertiges</t>
-  </si>
-  <si>
-    <t>1655</t>
-  </si>
-  <si>
-    <t>Evaluation visuelle des troubles orthoptiques et neurovisuels dans le cadre des troubles du neuro-développement (TNV - TND)</t>
-  </si>
-  <si>
-    <t>1656</t>
-  </si>
-  <si>
-    <t>Bilan de dépistage réfractif et de l'amblyopie</t>
-  </si>
-  <si>
-    <t>1657</t>
-  </si>
-  <si>
-    <t>Bilan visuel dans le cadre d'un renouvellement ou d'une adaptation de la correction optique (Protocole de coopération Renouvellement d'Optique (RNO))</t>
-  </si>
-  <si>
-    <t>1658</t>
-  </si>
-  <si>
-    <t>Exploration du sens chromatique</t>
-  </si>
-  <si>
-    <t>1659</t>
-  </si>
-  <si>
-    <t>Examen de la courbe d'adaptation à l'obscurité</t>
-  </si>
-  <si>
-    <t>1660</t>
-  </si>
-  <si>
-    <t>Protocole de dépistage de la rétinopathie diabétique</t>
-  </si>
-  <si>
-    <t>1661</t>
-  </si>
-  <si>
-    <t>Examen dépistage réfractif avec Photoscreener</t>
-  </si>
-  <si>
-    <t>1662</t>
-  </si>
-  <si>
-    <t>Bilan visuel primo-prescription ou renouvellement de la correction optique (lunettes, lentilles, souples) pour les patients de 16 ans à 42 ans</t>
-  </si>
-  <si>
-    <t>1663</t>
-  </si>
-  <si>
-    <t>Evaluation oculométrique par enregistrement – technique d'Eye tracking</t>
-  </si>
-  <si>
-    <t>1664</t>
-  </si>
-  <si>
-    <t>Evaluation et/ou prise en soins dans le cadre de particularités sensorielles et perceptives (profil sensoriel de DUNN, BOGDASHINA)</t>
-  </si>
-  <si>
-    <t>1665</t>
-  </si>
-  <si>
-    <t>Evaluation orthoptique et/ou prise en soins avec ajustement d'aide optique et nouvelle technologie associé à un handicap de la fonction visuelle (RV)</t>
-  </si>
-  <si>
-    <t>1666</t>
-  </si>
-  <si>
-    <t>Evaluation et suivi dans le cadre de l'adaptation du logement lors d'un handicap de la fonction visuelle</t>
-  </si>
-  <si>
-    <t>1667</t>
-  </si>
-  <si>
-    <t>Evaluation orthoptique de la fonction visuelle et/ou prise en soins dans le cadre de la conduite automobile</t>
-  </si>
-  <si>
-    <t>1668</t>
-  </si>
-  <si>
-    <t>Evaluation orthoptique de la fonction visuelle et/ou prise en soins dans le cadre de l'activité physique adaptée</t>
-  </si>
-  <si>
-    <t>1669</t>
-  </si>
-  <si>
-    <t>Evaluation et/ou prise en soins orthoptiques neurovisuels des troubles de la cognition visuelle</t>
-  </si>
-  <si>
-    <t>1670</t>
-  </si>
-  <si>
-    <t>Evaluation et/ou prise en soins de la rééducation neurovisuelle visuo-vestibulaire (vertiges)</t>
-  </si>
-  <si>
-    <t>1671</t>
-  </si>
-  <si>
-    <t>Dispensation médicamenteuse à domicile en cas d’impossibilité du patient à se déplacer</t>
-  </si>
-  <si>
-    <t>1672</t>
-  </si>
-  <si>
-    <t>Préparation des doses à administrer (PDA)</t>
-  </si>
-  <si>
-    <t>1673</t>
-  </si>
-  <si>
-    <t>Entretien pharmaceutique de la femme enceinte</t>
-  </si>
-  <si>
-    <t>1674</t>
-  </si>
-  <si>
-    <t>Entretien pharmaceutique du patient asthmatique sous corticostéroïdes inhalés (CSI)</t>
-  </si>
-  <si>
-    <t>1675</t>
-  </si>
-  <si>
-    <t>Entretien pharmaceutique du patient sous anticoagulant oral (AOD/AVK)</t>
-  </si>
-  <si>
-    <t>1676</t>
-  </si>
-  <si>
-    <t>Entretien pharmaceutique du patient sous anticancéreux oraux</t>
-  </si>
-  <si>
-    <t>1677</t>
-  </si>
-  <si>
-    <t>Entretien pharmaceutique du patient sous antalgique opioïde de pallier 2</t>
-  </si>
-  <si>
-    <t>1678</t>
-  </si>
-  <si>
-    <t>Entretien bilan partagé de médication</t>
-  </si>
-  <si>
-    <t>1679</t>
-  </si>
-  <si>
-    <t>Réseau France Santé</t>
-  </si>
-  <si>
-    <t>1680</t>
-  </si>
-  <si>
-    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
-  </si>
-  <si>
-    <t>1681</t>
-  </si>
-  <si>
-    <t>Orthèses et prothèses externes (orthopédie sur mesure)</t>
-  </si>
-  <si>
-    <t>1682</t>
-  </si>
-  <si>
-    <t>Orthèses et prothèses externes (de série)</t>
-  </si>
-  <si>
-    <t>1683</t>
-  </si>
-  <si>
-    <t>Optique lunetterie</t>
-  </si>
-  <si>
-    <t>1684</t>
-  </si>
-  <si>
-    <t>Audioprothèse</t>
-  </si>
-  <si>
-    <t>1685</t>
-  </si>
-  <si>
-    <t>Prise en charge de l’éruption cutanée vésiculeuse prurigineuse chez l’enfant (protocole de coopération)</t>
-  </si>
-  <si>
-    <t>1686</t>
-  </si>
-  <si>
-    <t>Renouvellement du traitement de la rhino-conjonctivite allergique saisonnière (protocole de coopération)</t>
-  </si>
-  <si>
-    <t>1687</t>
-  </si>
-  <si>
-    <t>Distribution de comprimés d’iode en application du Plan Particulier d’Intervention (PPI)</t>
-  </si>
-  <si>
-    <t>1688</t>
-  </si>
-  <si>
-    <t>Remise du kit de dépistage du cancer colorectal</t>
+    <t>Prise en charge spécialisée et continue rachis</t>
+  </si>
+  <si>
+    <t>1616</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée du pied diabétique de grade 2 et 3</t>
+  </si>
+  <si>
+    <t>1617</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée soins de support oncologie</t>
+  </si>
+  <si>
+    <t>1618</t>
+  </si>
+  <si>
+    <t>Orthoplastie (appareillage d’orteil)</t>
+  </si>
+  <si>
+    <t>1619</t>
+  </si>
+  <si>
+    <t>Orthonyxie (appareillage d’ongle)</t>
+  </si>
+  <si>
+    <t>1620</t>
+  </si>
+  <si>
+    <t>Onychoplastie (reconstruction de l’ongle)</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>Orthèse plantaire (semelle orthopédique)</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>Bilan diagnostique podologique de la prévention de la chute</t>
+  </si>
+  <si>
+    <t>1623</t>
+  </si>
+  <si>
+    <t>Rééducation du pied (sous la cheville)</t>
+  </si>
+  <si>
+    <t>1624</t>
+  </si>
+  <si>
+    <t>Contention nocturne</t>
+  </si>
+  <si>
+    <t>1625</t>
+  </si>
+  <si>
+    <t>Soin de pédicurie</t>
+  </si>
+  <si>
+    <t>1626</t>
+  </si>
+  <si>
+    <t>Traitement de la verrue plantaire par azote liquide</t>
+  </si>
+  <si>
+    <t>1627</t>
+  </si>
+  <si>
+    <t>Traitement sans douleur de l’ongle incarné par phénolisation (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1628</t>
+  </si>
+  <si>
+    <t>Prélèvement unguéal pour analyse biologique (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1629</t>
+  </si>
+  <si>
+    <t>Confection de semelle de comblement en polyuréthane (PU) pour amputation partielle du pied</t>
+  </si>
+  <si>
+    <t>1630</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et continue en pédopsychiatrie (dont équipe de liaison)</t>
+  </si>
+  <si>
+    <t>1631</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et continue SOS main</t>
   </si>
   <si>
     <t/>
@@ -8197,7 +7951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1308"/>
+  <dimension ref="A1:B1267"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -18329,343 +18083,15 @@
         <v>2556</v>
       </c>
       <c r="B1266" t="s" s="2">
-        <v>2557</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="s" s="2">
+        <v>2557</v>
+      </c>
+      <c r="B1267" t="s" s="2">
         <v>2558</v>
-      </c>
-      <c r="B1267" t="s" s="2">
-        <v>2559</v>
-      </c>
-    </row>
-    <row r="1268">
-      <c r="A1268" t="s" s="2">
-        <v>2560</v>
-      </c>
-      <c r="B1268" t="s" s="2">
-        <v>2561</v>
-      </c>
-    </row>
-    <row r="1269">
-      <c r="A1269" t="s" s="2">
-        <v>2562</v>
-      </c>
-      <c r="B1269" t="s" s="2">
-        <v>2563</v>
-      </c>
-    </row>
-    <row r="1270">
-      <c r="A1270" t="s" s="2">
-        <v>2564</v>
-      </c>
-      <c r="B1270" t="s" s="2">
-        <v>2565</v>
-      </c>
-    </row>
-    <row r="1271">
-      <c r="A1271" t="s" s="2">
-        <v>2566</v>
-      </c>
-      <c r="B1271" t="s" s="2">
-        <v>2567</v>
-      </c>
-    </row>
-    <row r="1272">
-      <c r="A1272" t="s" s="2">
-        <v>2568</v>
-      </c>
-      <c r="B1272" t="s" s="2">
-        <v>2569</v>
-      </c>
-    </row>
-    <row r="1273">
-      <c r="A1273" t="s" s="2">
-        <v>2570</v>
-      </c>
-      <c r="B1273" t="s" s="2">
-        <v>2571</v>
-      </c>
-    </row>
-    <row r="1274">
-      <c r="A1274" t="s" s="2">
-        <v>2572</v>
-      </c>
-      <c r="B1274" t="s" s="2">
-        <v>2573</v>
-      </c>
-    </row>
-    <row r="1275">
-      <c r="A1275" t="s" s="2">
-        <v>2574</v>
-      </c>
-      <c r="B1275" t="s" s="2">
-        <v>2575</v>
-      </c>
-    </row>
-    <row r="1276">
-      <c r="A1276" t="s" s="2">
-        <v>2576</v>
-      </c>
-      <c r="B1276" t="s" s="2">
-        <v>2577</v>
-      </c>
-    </row>
-    <row r="1277">
-      <c r="A1277" t="s" s="2">
-        <v>2578</v>
-      </c>
-      <c r="B1277" t="s" s="2">
-        <v>2579</v>
-      </c>
-    </row>
-    <row r="1278">
-      <c r="A1278" t="s" s="2">
-        <v>2580</v>
-      </c>
-      <c r="B1278" t="s" s="2">
-        <v>2581</v>
-      </c>
-    </row>
-    <row r="1279">
-      <c r="A1279" t="s" s="2">
-        <v>2582</v>
-      </c>
-      <c r="B1279" t="s" s="2">
-        <v>2583</v>
-      </c>
-    </row>
-    <row r="1280">
-      <c r="A1280" t="s" s="2">
-        <v>2584</v>
-      </c>
-      <c r="B1280" t="s" s="2">
-        <v>2585</v>
-      </c>
-    </row>
-    <row r="1281">
-      <c r="A1281" t="s" s="2">
-        <v>2586</v>
-      </c>
-      <c r="B1281" t="s" s="2">
-        <v>2587</v>
-      </c>
-    </row>
-    <row r="1282">
-      <c r="A1282" t="s" s="2">
-        <v>2588</v>
-      </c>
-      <c r="B1282" t="s" s="2">
-        <v>2589</v>
-      </c>
-    </row>
-    <row r="1283">
-      <c r="A1283" t="s" s="2">
-        <v>2590</v>
-      </c>
-      <c r="B1283" t="s" s="2">
-        <v>2591</v>
-      </c>
-    </row>
-    <row r="1284">
-      <c r="A1284" t="s" s="2">
-        <v>2592</v>
-      </c>
-      <c r="B1284" t="s" s="2">
-        <v>2593</v>
-      </c>
-    </row>
-    <row r="1285">
-      <c r="A1285" t="s" s="2">
-        <v>2594</v>
-      </c>
-      <c r="B1285" t="s" s="2">
-        <v>2595</v>
-      </c>
-    </row>
-    <row r="1286">
-      <c r="A1286" t="s" s="2">
-        <v>2596</v>
-      </c>
-      <c r="B1286" t="s" s="2">
-        <v>2597</v>
-      </c>
-    </row>
-    <row r="1287">
-      <c r="A1287" t="s" s="2">
-        <v>2598</v>
-      </c>
-      <c r="B1287" t="s" s="2">
-        <v>2599</v>
-      </c>
-    </row>
-    <row r="1288">
-      <c r="A1288" t="s" s="2">
-        <v>2600</v>
-      </c>
-      <c r="B1288" t="s" s="2">
-        <v>2601</v>
-      </c>
-    </row>
-    <row r="1289">
-      <c r="A1289" t="s" s="2">
-        <v>2602</v>
-      </c>
-      <c r="B1289" t="s" s="2">
-        <v>2603</v>
-      </c>
-    </row>
-    <row r="1290">
-      <c r="A1290" t="s" s="2">
-        <v>2604</v>
-      </c>
-      <c r="B1290" t="s" s="2">
-        <v>2605</v>
-      </c>
-    </row>
-    <row r="1291">
-      <c r="A1291" t="s" s="2">
-        <v>2606</v>
-      </c>
-      <c r="B1291" t="s" s="2">
-        <v>2607</v>
-      </c>
-    </row>
-    <row r="1292">
-      <c r="A1292" t="s" s="2">
-        <v>2608</v>
-      </c>
-      <c r="B1292" t="s" s="2">
-        <v>2609</v>
-      </c>
-    </row>
-    <row r="1293">
-      <c r="A1293" t="s" s="2">
-        <v>2610</v>
-      </c>
-      <c r="B1293" t="s" s="2">
-        <v>2611</v>
-      </c>
-    </row>
-    <row r="1294">
-      <c r="A1294" t="s" s="2">
-        <v>2612</v>
-      </c>
-      <c r="B1294" t="s" s="2">
-        <v>2613</v>
-      </c>
-    </row>
-    <row r="1295">
-      <c r="A1295" t="s" s="2">
-        <v>2614</v>
-      </c>
-      <c r="B1295" t="s" s="2">
-        <v>2615</v>
-      </c>
-    </row>
-    <row r="1296">
-      <c r="A1296" t="s" s="2">
-        <v>2616</v>
-      </c>
-      <c r="B1296" t="s" s="2">
-        <v>2617</v>
-      </c>
-    </row>
-    <row r="1297">
-      <c r="A1297" t="s" s="2">
-        <v>2618</v>
-      </c>
-      <c r="B1297" t="s" s="2">
-        <v>2619</v>
-      </c>
-    </row>
-    <row r="1298">
-      <c r="A1298" t="s" s="2">
-        <v>2620</v>
-      </c>
-      <c r="B1298" t="s" s="2">
-        <v>2621</v>
-      </c>
-    </row>
-    <row r="1299">
-      <c r="A1299" t="s" s="2">
-        <v>2622</v>
-      </c>
-      <c r="B1299" t="s" s="2">
-        <v>2623</v>
-      </c>
-    </row>
-    <row r="1300">
-      <c r="A1300" t="s" s="2">
-        <v>2624</v>
-      </c>
-      <c r="B1300" t="s" s="2">
-        <v>2625</v>
-      </c>
-    </row>
-    <row r="1301">
-      <c r="A1301" t="s" s="2">
-        <v>2626</v>
-      </c>
-      <c r="B1301" t="s" s="2">
-        <v>2627</v>
-      </c>
-    </row>
-    <row r="1302">
-      <c r="A1302" t="s" s="2">
-        <v>2628</v>
-      </c>
-      <c r="B1302" t="s" s="2">
-        <v>2629</v>
-      </c>
-    </row>
-    <row r="1303">
-      <c r="A1303" t="s" s="2">
-        <v>2630</v>
-      </c>
-      <c r="B1303" t="s" s="2">
-        <v>2631</v>
-      </c>
-    </row>
-    <row r="1304">
-      <c r="A1304" t="s" s="2">
-        <v>2632</v>
-      </c>
-      <c r="B1304" t="s" s="2">
-        <v>2633</v>
-      </c>
-    </row>
-    <row r="1305">
-      <c r="A1305" t="s" s="2">
-        <v>2634</v>
-      </c>
-      <c r="B1305" t="s" s="2">
-        <v>2635</v>
-      </c>
-    </row>
-    <row r="1306">
-      <c r="A1306" t="s" s="2">
-        <v>2636</v>
-      </c>
-      <c r="B1306" t="s" s="2">
-        <v>2637</v>
-      </c>
-    </row>
-    <row r="1307">
-      <c r="A1307" t="s" s="2">
-        <v>2638</v>
-      </c>
-      <c r="B1307" t="s" s="2">
-        <v>2638</v>
-      </c>
-    </row>
-    <row r="1308">
-      <c r="A1308" t="s" s="2">
-        <v>2639</v>
-      </c>
-      <c r="B1308" t="s" s="2">
-        <v>2640</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2643" uniqueCount="2641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="2705">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -714,7 +714,7 @@
     <t>0182</t>
   </si>
   <si>
-    <t>Programme d’ETP labellisée - Asthme</t>
+    <t>Programme d'ETP labellisée - Asthme (école de l'asthme)</t>
   </si>
   <si>
     <t>0183</t>
@@ -3228,7 +3228,7 @@
     <t>0822</t>
   </si>
   <si>
-    <t>Groupes de soutien et d'échange</t>
+    <t>Groupes de soutien et d'échange ouvert aux aidants</t>
   </si>
   <si>
     <t>0823</t>
@@ -3270,7 +3270,7 @@
     <t>0829</t>
   </si>
   <si>
-    <t>Prise en charge de l'apnée du sommeil</t>
+    <t>Prise en charge de l'apnée du sommeil par appareillage ventilatoire</t>
   </si>
   <si>
     <t>0830</t>
@@ -3648,7 +3648,7 @@
     <t>0897</t>
   </si>
   <si>
-    <t>Drainage Vaccination épidémie Grippe</t>
+    <t>Vaccination épidémie Grippe</t>
   </si>
   <si>
     <t>0898</t>
@@ -5664,7 +5664,7 @@
     <t>1276</t>
   </si>
   <si>
-    <t>Enregistrement polygraphique dans le cadre du syndrome d'apnées obstructives du sommeil (SAOS)</t>
+    <t>Enregistrement polygraphique dans le cadre d'une forte suspicion de Syndrome d'Apnées/Hypopnées Obstructives du Sommeil (SAHOS)</t>
   </si>
   <si>
     <t>1277</t>
@@ -6603,6 +6603,12 @@
     <t>Santé environnementale</t>
   </si>
   <si>
+    <t>1449</t>
+  </si>
+  <si>
+    <t>Thérapie cellulaire des brûlures radiques par Cellules Souches Mésenchymateuses (CSM)</t>
+  </si>
+  <si>
     <t>1450</t>
   </si>
   <si>
@@ -7386,205 +7392,301 @@
     <t>1582</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en cardiologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en cardiologie</t>
   </si>
   <si>
     <t>1583</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie cardiaque et gros vaisseaux</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie cardiaque et gros vaisseaux</t>
   </si>
   <si>
     <t>1584</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie digestive et viscérale</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie digestive et viscérale</t>
   </si>
   <si>
     <t>1585</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie maxillo-faciale et stomatologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie maxillo-faciale et stomatologie</t>
   </si>
   <si>
     <t>1586</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1587</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique orthopédique et traumatologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie pédiatrique orthopédique et traumatologie</t>
   </si>
   <si>
     <t>1588</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie pédiatrique viscérale et digestive</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie pédiatrique viscérale et digestive</t>
   </si>
   <si>
     <t>1589</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie thoracique et pulmonaire</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie thoracique et pulmonaire</t>
   </si>
   <si>
     <t>1590</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie vasculaire</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie vasculaire</t>
   </si>
   <si>
     <t>1591</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en dermatologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en dermatologie</t>
   </si>
   <si>
     <t>1592</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en endocrinologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en endocrinologie</t>
   </si>
   <si>
     <t>1593</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gériatrie (gérontologie)</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en gériatrie (gérontologie)</t>
   </si>
   <si>
     <t>1594</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en gynécologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en gynécologie</t>
   </si>
   <si>
     <t>1595</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hématologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en hématologie</t>
   </si>
   <si>
     <t>1596</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en hépato-gastro-entérologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en hépato-gastro-entérologie</t>
   </si>
   <si>
     <t>1597</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en maladies infectieuses et tropicales</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en maladies infectieuses et tropicales</t>
   </si>
   <si>
     <t>1598</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine interne</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en médecine interne</t>
   </si>
   <si>
     <t>1599</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en médecine vasculaire</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en médecine vasculaire</t>
   </si>
   <si>
     <t>1600</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en néphrologie (dont dialyse)</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en néphrologie (dont dialyse)</t>
   </si>
   <si>
     <t>1601</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurochirurgie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en neurochirurgie</t>
   </si>
   <si>
     <t>1602</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en neurologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en neurologie</t>
   </si>
   <si>
     <t>1603</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oncologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en oncologie</t>
   </si>
   <si>
     <t>1604</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en ophtalmologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en ophtalmologie</t>
   </si>
   <si>
     <t>1605</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en oto-rhino-laryngologie (ORL) et chirurgie cervico-faciale</t>
   </si>
   <si>
     <t>1606</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pédiatrie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en pédiatrie</t>
   </si>
   <si>
     <t>1607</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en pneumologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en pneumologie</t>
   </si>
   <si>
     <t>1608</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en rhumatologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en rhumatologie</t>
   </si>
   <si>
     <t>1609</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en urologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en urologie</t>
   </si>
   <si>
     <t>1610</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en caisson oxygène hyperbare</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en caisson oxygène hyperbare</t>
   </si>
   <si>
     <t>1611</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en chirurgie de la main SOS main</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie de la main</t>
   </si>
   <si>
     <t>1612</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en odontologie</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en odontologie</t>
   </si>
   <si>
     <t>1613</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en psychiatrie (dont équipe de liaison)</t>
+    <t>Prise en charge spécialisée et permanente en psychiatrie (dont équipe de liaison)</t>
   </si>
   <si>
     <t>1614</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) en radiologie interventionnelle</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en radiologie interventionnelle</t>
   </si>
   <si>
     <t>1615</t>
   </si>
   <si>
-    <t>Prise en charge spécialisée et en permanence (24h/24 – 7j/7) rachis</t>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) en chirurgie du rachis</t>
+  </si>
+  <si>
+    <t>1616</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée du pied diabétique de grade 2 et 3</t>
+  </si>
+  <si>
+    <t>1617</t>
+  </si>
+  <si>
+    <t>Pédicurie-podologie conventionnée soins de support oncologie</t>
+  </si>
+  <si>
+    <t>1618</t>
+  </si>
+  <si>
+    <t>Orthoplastie (appareillage d’orteil)</t>
+  </si>
+  <si>
+    <t>1619</t>
+  </si>
+  <si>
+    <t>Orthonyxie (appareillage d’ongle)</t>
+  </si>
+  <si>
+    <t>1620</t>
+  </si>
+  <si>
+    <t>Onychoplastie (reconstruction de l’ongle)</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>Orthèse plantaire (semelle orthopédique)</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>Bilan diagnostique podologique de la prévention de la chute</t>
+  </si>
+  <si>
+    <t>1623</t>
+  </si>
+  <si>
+    <t>Rééducation du pied (sous la cheville)</t>
+  </si>
+  <si>
+    <t>1624</t>
+  </si>
+  <si>
+    <t>Contention nocturne</t>
+  </si>
+  <si>
+    <t>1625</t>
+  </si>
+  <si>
+    <t>Soin de pédicurie</t>
+  </si>
+  <si>
+    <t>1626</t>
+  </si>
+  <si>
+    <t>Traitement de la verrue plantaire par azote liquide</t>
+  </si>
+  <si>
+    <t>1627</t>
+  </si>
+  <si>
+    <t>Traitement sans douleur de l’ongle incarné par phénolisation (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1628</t>
+  </si>
+  <si>
+    <t>Prélèvement unguéal pour analyse biologique (protocole de coopération)</t>
+  </si>
+  <si>
+    <t>1629</t>
+  </si>
+  <si>
+    <t>Confection de semelle de comblement en polyuréthane (PU) pour amputation partielle du pied</t>
+  </si>
+  <si>
+    <t>1630</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et permanente en pédopsychiatrie (dont équipe de liaison)</t>
+  </si>
+  <si>
+    <t>1631</t>
+  </si>
+  <si>
+    <t>Prise en charge spécialisée et permanente (dont PDSES) SOS main (agrément FESUM)</t>
   </si>
   <si>
     <t>1632</t>
@@ -7927,6 +8029,96 @@
   </si>
   <si>
     <t>Remise du kit de dépistage du cancer colorectal</t>
+  </si>
+  <si>
+    <t>1689</t>
+  </si>
+  <si>
+    <t>Test de Maintien de l’Eveil (TME)</t>
+  </si>
+  <si>
+    <t>1690</t>
+  </si>
+  <si>
+    <t>Test Itératif de Latence d'Endormissement (TILE)</t>
+  </si>
+  <si>
+    <t>1691</t>
+  </si>
+  <si>
+    <t>Prise en charge de l’insomnie</t>
+  </si>
+  <si>
+    <t>1692</t>
+  </si>
+  <si>
+    <t>Prise en charge des troubles moteurs (syndrome des jambes sans repos)</t>
+  </si>
+  <si>
+    <t>1693</t>
+  </si>
+  <si>
+    <t>Prise en charge de parasomnie (somnambulisme)</t>
+  </si>
+  <si>
+    <t>1694</t>
+  </si>
+  <si>
+    <t>Prise en charge des hypersomnies</t>
+  </si>
+  <si>
+    <t>1695</t>
+  </si>
+  <si>
+    <t>Prise en charge des troubles circadiens</t>
+  </si>
+  <si>
+    <t>1696</t>
+  </si>
+  <si>
+    <t>Prise en charge des troubles du sommeil avec trouble neurologique complexe</t>
+  </si>
+  <si>
+    <t>1697</t>
+  </si>
+  <si>
+    <t>Prise en charge des troubles du sommeil avec trouble respiratoire complexe</t>
+  </si>
+  <si>
+    <t>1698</t>
+  </si>
+  <si>
+    <t>Centre de Référence d'Infection Ostéo-Articulaire/ Complexes (CRIOA/ C) - Niveau 1 "coordonnateur"</t>
+  </si>
+  <si>
+    <t>1699</t>
+  </si>
+  <si>
+    <t>Centre de Référence d'Infection Ostéo-Articulaire/ Complexes (CRIOA/ C) - Niveau 2 "correspondant"</t>
+  </si>
+  <si>
+    <t>1700</t>
+  </si>
+  <si>
+    <t>Accréditation par la Société Française de Recherche en Médecine du Sommeil (SFRMS)</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>Prise en charge de nouveau patient en tant que médecin traitant</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>Accompagnement à l'essai de fauteuil roulant</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>Groupe (ou stage) psycho-éducatif de responsabilisation pour prévention de la violence et/ou de sa récidive</t>
   </si>
   <si>
     <t/>
@@ -8197,7 +8389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1308"/>
+  <dimension ref="A1:B1340"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -18657,15 +18849,271 @@
         <v>2638</v>
       </c>
       <c r="B1307" t="s" s="2">
-        <v>2638</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="s" s="2">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="B1308" t="s" s="2">
-        <v>2640</v>
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="s" s="2">
+        <v>2642</v>
+      </c>
+      <c r="B1309" t="s" s="2">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="s" s="2">
+        <v>2644</v>
+      </c>
+      <c r="B1310" t="s" s="2">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="s" s="2">
+        <v>2646</v>
+      </c>
+      <c r="B1311" t="s" s="2">
+        <v>2647</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="s" s="2">
+        <v>2648</v>
+      </c>
+      <c r="B1312" t="s" s="2">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="s" s="2">
+        <v>2650</v>
+      </c>
+      <c r="B1313" t="s" s="2">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="s" s="2">
+        <v>2652</v>
+      </c>
+      <c r="B1314" t="s" s="2">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="s" s="2">
+        <v>2654</v>
+      </c>
+      <c r="B1315" t="s" s="2">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="s" s="2">
+        <v>2656</v>
+      </c>
+      <c r="B1316" t="s" s="2">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="s" s="2">
+        <v>2658</v>
+      </c>
+      <c r="B1317" t="s" s="2">
+        <v>2659</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="s" s="2">
+        <v>2660</v>
+      </c>
+      <c r="B1318" t="s" s="2">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="s" s="2">
+        <v>2662</v>
+      </c>
+      <c r="B1319" t="s" s="2">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="s" s="2">
+        <v>2664</v>
+      </c>
+      <c r="B1320" t="s" s="2">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="s" s="2">
+        <v>2666</v>
+      </c>
+      <c r="B1321" t="s" s="2">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="s" s="2">
+        <v>2668</v>
+      </c>
+      <c r="B1322" t="s" s="2">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="s" s="2">
+        <v>2670</v>
+      </c>
+      <c r="B1323" t="s" s="2">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="s" s="2">
+        <v>2672</v>
+      </c>
+      <c r="B1324" t="s" s="2">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="s" s="2">
+        <v>2674</v>
+      </c>
+      <c r="B1325" t="s" s="2">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="s" s="2">
+        <v>2676</v>
+      </c>
+      <c r="B1326" t="s" s="2">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="s" s="2">
+        <v>2678</v>
+      </c>
+      <c r="B1327" t="s" s="2">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="s" s="2">
+        <v>2680</v>
+      </c>
+      <c r="B1328" t="s" s="2">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="s" s="2">
+        <v>2682</v>
+      </c>
+      <c r="B1329" t="s" s="2">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="s" s="2">
+        <v>2684</v>
+      </c>
+      <c r="B1330" t="s" s="2">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="s" s="2">
+        <v>2686</v>
+      </c>
+      <c r="B1331" t="s" s="2">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="s" s="2">
+        <v>2688</v>
+      </c>
+      <c r="B1332" t="s" s="2">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="s" s="2">
+        <v>2690</v>
+      </c>
+      <c r="B1333" t="s" s="2">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="s" s="2">
+        <v>2692</v>
+      </c>
+      <c r="B1334" t="s" s="2">
+        <v>2693</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="s" s="2">
+        <v>2694</v>
+      </c>
+      <c r="B1335" t="s" s="2">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="s" s="2">
+        <v>2696</v>
+      </c>
+      <c r="B1336" t="s" s="2">
+        <v>2697</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="s" s="2">
+        <v>2698</v>
+      </c>
+      <c r="B1337" t="s" s="2">
+        <v>2699</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="s" s="2">
+        <v>2700</v>
+      </c>
+      <c r="B1338" t="s" s="2">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="s" s="2">
+        <v>2702</v>
+      </c>
+      <c r="B1339" t="s" s="2">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="s" s="2">
+        <v>2703</v>
+      </c>
+      <c r="B1340" t="s" s="2">
+        <v>2704</v>
       </c>
     </row>
   </sheetData>
